--- a/data-manipulation-scripts/sheets-cleanup/sheets/GUIDAO - 27_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/GUIDAO - 27_01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -55,9 +55,6 @@
     <t>GUIDAO CROMADO (C/ SUPORTE PESO) COMETA YES125 2008</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>7000000056635</t>
   </si>
   <si>
@@ -97,7 +94,7 @@
     <t>7908342736805</t>
   </si>
   <si>
-    <t xml:space="preserve">GUIDAO PRETO ( C/ SUPORTE PESO) MX1 </t>
+    <t>GUIDAO PRETO ( C/ SUPORTE PESO) MX1 TITAN150 2014</t>
   </si>
   <si>
     <t>7908285479081</t>
@@ -134,6 +131,9 @@
   </si>
   <si>
     <t>GUIDAO PRETO NXR15-150</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -445,7 +445,9 @@
       <c r="C2" s="2">
         <v>6.0</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="2">
+        <v>80.0</v>
+      </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
@@ -460,7 +462,9 @@
       <c r="C3" s="2">
         <v>2.0</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="2">
+        <v>100.0</v>
+      </c>
       <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
@@ -492,8 +496,8 @@
       <c r="C5" s="2">
         <v>1.0</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
+      <c r="D5" s="2">
+        <v>75.0</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>7</v>
@@ -501,10 +505,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="C6" s="2">
         <v>2.0</v>
@@ -518,25 +522,27 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="C7" s="2">
         <v>1.0</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="2">
+        <v>100.0</v>
+      </c>
       <c r="E7" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="C8" s="2">
         <v>3.0</v>
@@ -550,40 +556,44 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="C9" s="2">
         <v>1.0</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="2">
+        <v>75.0</v>
+      </c>
       <c r="E9" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="C10" s="2">
         <v>1.0</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="2">
+        <v>75.0</v>
+      </c>
       <c r="E10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="C11" s="2">
         <v>2.0</v>
@@ -597,25 +607,27 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="C12" s="2">
         <v>2.0</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="2">
+        <v>80.0</v>
+      </c>
       <c r="E12" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="C13" s="2">
         <v>1.0</v>
@@ -629,10 +641,10 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="C14" s="2">
         <v>1.0</v>
@@ -646,10 +658,10 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="C15" s="2">
         <v>2.0</v>
@@ -663,52 +675,58 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="C16" s="2">
         <v>1.0</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="2">
+        <v>75.0</v>
+      </c>
       <c r="E16" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="C17" s="2">
         <v>1.0</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="2">
+        <v>80.0</v>
+      </c>
       <c r="E17" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="C18" s="2">
         <v>2.0</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="2">
+        <v>80.0</v>
+      </c>
       <c r="E18" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
